--- a/data/_master_summary.xlsx
+++ b/data/_master_summary.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t xml:space="preserve">Kingdom</t>
   </si>
@@ -52,10 +52,13 @@
     <t xml:space="preserve">Commoner</t>
   </si>
   <si>
+    <t xml:space="preserve">Elite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adventurer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">God</t>
   </si>
 </sst>
 </file>
@@ -256,7 +259,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -272,7 +275,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -552,37 +555,40 @@
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="str">
-        <f aca="false">IFERROR((B3/$N$6),"")</f>
+        <f aca="false">IFERROR((B3/$N$7),"")</f>
         <v/>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="8" t="str">
-        <f aca="false">IFERROR((D3/$N$6),"")</f>
+        <f aca="false">IFERROR((D3/$N$7),"")</f>
         <v/>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="8" t="str">
-        <f aca="false">IFERROR((F3/$N$6),"")</f>
+        <f aca="false">IFERROR((F3/$N$7),"")</f>
         <v/>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="8" t="str">
-        <f aca="false">IFERROR((H3/$N$6),"")</f>
+        <f aca="false">IFERROR((H3/$N$7),"")</f>
         <v/>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="8" t="str">
-        <f aca="false">IFERROR((J3/$N$6),"")</f>
+        <f aca="false">IFERROR((J3/$N$7),"")</f>
         <v/>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="8" t="str">
-        <f aca="false">IFERROR((L3/$N$6),"")</f>
-        <v/>
-      </c>
-      <c r="N3" s="9"/>
+        <f aca="false">IFERROR((L3/$N$7),"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="9" t="n">
+        <f aca="false">SUM(L3,J3,H3,F3,D3,B3)</f>
+        <v>0</v>
+      </c>
       <c r="O3" s="10" t="str">
-        <f aca="false">IFERROR((N3/$N$6),"")</f>
+        <f aca="false">IFERROR((N3/$N$7),"")</f>
         <v/>
       </c>
     </row>
@@ -592,37 +598,40 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="12" t="str">
-        <f aca="false">IFERROR((B4/$N$6),"")</f>
+        <f aca="false">IFERROR((B4/$N$7),"")</f>
         <v/>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="12" t="str">
-        <f aca="false">IFERROR((D4/$N$6),"")</f>
+        <f aca="false">IFERROR((D4/$N$7),"")</f>
         <v/>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="str">
-        <f aca="false">IFERROR((F4/$N$6),"")</f>
+        <f aca="false">IFERROR((F4/$N$7),"")</f>
         <v/>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="str">
-        <f aca="false">IFERROR((H4/$N$6),"")</f>
+        <f aca="false">IFERROR((H4/$N$7),"")</f>
         <v/>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="12" t="str">
-        <f aca="false">IFERROR((J4/$N$6),"")</f>
+        <f aca="false">IFERROR((J4/$N$7),"")</f>
         <v/>
       </c>
       <c r="L4" s="11"/>
       <c r="M4" s="12" t="str">
-        <f aca="false">IFERROR((L4/$N$6),"")</f>
-        <v/>
-      </c>
-      <c r="N4" s="13"/>
+        <f aca="false">IFERROR((L4/$N$7),"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="13" t="n">
+        <f aca="false">SUM(L4,J4,H4,F4,D4,B4)</f>
+        <v>0</v>
+      </c>
       <c r="O4" s="14" t="str">
-        <f aca="false">IFERROR((N4/$N$6),"")</f>
+        <f aca="false">IFERROR((N4/$N$7),"")</f>
         <v/>
       </c>
     </row>
@@ -632,96 +641,146 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="str">
-        <f aca="false">IFERROR((B5/$N$6),"")</f>
+        <f aca="false">IFERROR((B5/$N$7),"")</f>
         <v/>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="8" t="str">
-        <f aca="false">IFERROR((D5/$N$6),"")</f>
+        <f aca="false">IFERROR((D5/$N$7),"")</f>
         <v/>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="8" t="str">
-        <f aca="false">IFERROR((F5/$N$6),"")</f>
+        <f aca="false">IFERROR((F5/$N$7),"")</f>
         <v/>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="8" t="str">
-        <f aca="false">IFERROR((H5/$N$6),"")</f>
+        <f aca="false">IFERROR((H5/$N$7),"")</f>
         <v/>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="8" t="str">
-        <f aca="false">IFERROR((J5/$N$6),"")</f>
+        <f aca="false">IFERROR((J5/$N$7),"")</f>
         <v/>
       </c>
       <c r="L5" s="7"/>
       <c r="M5" s="8" t="str">
-        <f aca="false">IFERROR((L5/$N$6),"")</f>
-        <v/>
-      </c>
-      <c r="N5" s="9"/>
+        <f aca="false">IFERROR((L5/$N$7),"")</f>
+        <v/>
+      </c>
+      <c r="N5" s="9" t="n">
+        <f aca="false">SUM(L5,J5,H5,F5,D5,B5)</f>
+        <v>0</v>
+      </c>
       <c r="O5" s="10" t="str">
-        <f aca="false">IFERROR((N5/$N$6),"")</f>
+        <f aca="false">IFERROR((N5/$N$7),"")</f>
         <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12" t="str">
+        <f aca="false">IFERROR((B6/$N$7),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12" t="str">
+        <f aca="false">IFERROR((D6/$N$7),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="12" t="str">
+        <f aca="false">IFERROR((F6/$N$7),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12" t="str">
+        <f aca="false">IFERROR((H6/$N$7),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="12" t="str">
+        <f aca="false">IFERROR((J6/$N$7),"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="11"/>
+      <c r="M6" s="12" t="str">
+        <f aca="false">IFERROR((L6/$N$7),"")</f>
+        <v/>
+      </c>
+      <c r="N6" s="13" t="n">
+        <f aca="false">SUM(L6,J6,H6,F6,D6,B6)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="14" t="str">
+        <f aca="false">IFERROR((N6/$N$7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17" t="str">
-        <f aca="false">IFERROR((B6/$N$6),"")</f>
-        <v/>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17" t="str">
-        <f aca="false">IFERROR((D6/$N$6),"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17" t="str">
-        <f aca="false">IFERROR((F6/$N$6),"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="17" t="str">
-        <f aca="false">IFERROR((H6/$N$6),"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17" t="str">
-        <f aca="false">IFERROR((J6/$N$6),"")</f>
-        <v/>
-      </c>
-      <c r="L6" s="16"/>
-      <c r="M6" s="17" t="str">
-        <f aca="false">IFERROR((L6/$N$6),"")</f>
-        <v/>
-      </c>
-      <c r="N6" s="18"/>
-      <c r="O6" s="19" t="str">
-        <f aca="false">IFERROR((N6/$N$6),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
+      <c r="B7" s="16" t="n">
+        <f aca="false">SUM(B3:B6)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <f aca="false">IFERROR((B7/$N$7),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <f aca="false">SUM(D3:D6)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <f aca="false">IFERROR((D7/$N$7),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <f aca="false">SUM(F3:F6)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <f aca="false">IFERROR((F7/$N$7),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <f aca="false">SUM(H3:H6)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <f aca="false">IFERROR((H7/$N$7),0)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <f aca="false">SUM(J3:J6)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <f aca="false">IFERROR((J7/$N$7),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <f aca="false">SUM(L3:L6)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="17" t="n">
+        <f aca="false">IFERROR((L7/$N$7),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="18" t="n">
+        <f aca="false">SUM(N3:N6)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="19" t="n">
+        <f aca="false">IFERROR((N7/$N$7),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
